--- a/resource/groundTruths/architecture/CF_M06_ground_truth_architecture.xlsx
+++ b/resource/groundTruths/architecture/CF_M06_ground_truth_architecture.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/oguzarslan/Desktop/upc/semester-4/Thesis/MappingGenerator/resource/groundTruths/architecture/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{299BF1C6-7DDB-1147-B9E2-302A4B2CAE45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6732B92F-BEC9-3547-915A-5DF657E460CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="17400" yWindow="900" windowWidth="11840" windowHeight="16640" xr2:uid="{1045ED32-4CBD-334F-AA9D-ECDD290D947C}"/>
+    <workbookView xWindow="17400" yWindow="900" windowWidth="11840" windowHeight="16640" activeTab="1" xr2:uid="{1045ED32-4CBD-334F-AA9D-ECDD290D947C}"/>
   </bookViews>
   <sheets>
     <sheet name="Architectural Units" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="110">
   <si>
     <t>Document ID</t>
   </si>
@@ -365,6 +365,9 @@
   </si>
   <si>
     <t>CF_M06_AU02, CF_M06_AU23</t>
+  </si>
+  <si>
+    <t>Fixed Type</t>
   </si>
 </sst>
 </file>
@@ -755,10 +758,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85D170AC-8FA6-684F-BE5D-AC7530795B70}">
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:H27"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:7" ht="28" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" ht="28" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -780,8 +783,11 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" ht="34" x14ac:dyDescent="0.2">
+      <c r="H1" s="1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="34" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -801,7 +807,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -821,7 +827,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>7</v>
       </c>
@@ -844,7 +850,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -867,7 +873,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -890,7 +896,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>7</v>
       </c>
@@ -913,7 +919,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -936,7 +942,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -959,7 +965,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>7</v>
       </c>
@@ -982,7 +988,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>7</v>
       </c>
@@ -1002,7 +1008,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>7</v>
       </c>
@@ -1019,7 +1025,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>7</v>
       </c>
@@ -1039,7 +1045,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>7</v>
       </c>
@@ -1059,7 +1065,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>7</v>
       </c>
@@ -1082,7 +1088,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>7</v>
       </c>
@@ -1338,10 +1344,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B3416A1-E7A8-0840-921D-A3BE7B012A10}">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:7" ht="28" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" ht="28" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1363,8 +1369,11 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H1" s="1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -1387,7 +1396,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -1410,7 +1419,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>7</v>
       </c>
@@ -1433,7 +1442,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -1456,7 +1465,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>7</v>
       </c>

--- a/resource/groundTruths/architecture/CF_M06_ground_truth_architecture.xlsx
+++ b/resource/groundTruths/architecture/CF_M06_ground_truth_architecture.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/oguzarslan/Desktop/upc/semester-4/Thesis/MappingGenerator/resource/groundTruths/architecture/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6732B92F-BEC9-3547-915A-5DF657E460CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{789E0B1D-D473-1245-B2E7-C95D9D496FBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="17400" yWindow="900" windowWidth="11840" windowHeight="16640" activeTab="1" xr2:uid="{1045ED32-4CBD-334F-AA9D-ECDD290D947C}"/>
+    <workbookView xWindow="17400" yWindow="900" windowWidth="11840" windowHeight="16640" xr2:uid="{1045ED32-4CBD-334F-AA9D-ECDD290D947C}"/>
   </bookViews>
   <sheets>
     <sheet name="Architectural Units" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="125">
   <si>
     <t>Document ID</t>
   </si>
@@ -174,9 +174,6 @@
   </si>
   <si>
     <t>Architectural Pattern</t>
-  </si>
-  <si>
-    <t>3-layer model</t>
   </si>
   <si>
     <t>This architecture follows the 3-layer model</t>
@@ -368,6 +365,54 @@
   </si>
   <si>
     <t>Fixed Type</t>
+  </si>
+  <si>
+    <t>This will interact with the Waapiti API using HTTP requests.</t>
+  </si>
+  <si>
+    <t>CF_M06_AU01, CF_M06_AU02</t>
+  </si>
+  <si>
+    <t>CF_M06_AU27</t>
+  </si>
+  <si>
+    <t>It is the server responsible for communicating with the database and other services hosted on AWS.</t>
+  </si>
+  <si>
+    <t>CF_M06_AU02, CF_M06_AU05</t>
+  </si>
+  <si>
+    <t>CF_M06_AU28</t>
+  </si>
+  <si>
+    <t>Three Layers</t>
+  </si>
+  <si>
+    <t>HTTP</t>
+  </si>
+  <si>
+    <t>CF_M06_AU29</t>
+  </si>
+  <si>
+    <t>Socket</t>
+  </si>
+  <si>
+    <t>CF_M06_AU30</t>
+  </si>
+  <si>
+    <t>CF_M06_AU31</t>
+  </si>
+  <si>
+    <t>This functionality connects via socket [25] with the server and displays</t>
+  </si>
+  <si>
+    <t>the content according to the messages that it sends.</t>
+  </si>
+  <si>
+    <t>CF_M06_AU23, CF_M06_AU02</t>
+  </si>
+  <si>
+    <t>This is the central hub that manages all the data flow. It notifies the Stores when the state needs to be modified.</t>
   </si>
 </sst>
 </file>
@@ -758,7 +803,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85D170AC-8FA6-684F-BE5D-AC7530795B70}">
-  <dimension ref="A1:H27"/>
+  <dimension ref="A1:H32"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:8" ht="28" x14ac:dyDescent="0.2">
@@ -784,7 +829,7 @@
         <v>6</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="34" x14ac:dyDescent="0.2">
@@ -815,13 +860,13 @@
         <v>9</v>
       </c>
       <c r="C3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D3" t="s">
         <v>43</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G3">
         <v>45</v>
@@ -835,13 +880,13 @@
         <v>10</v>
       </c>
       <c r="C4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F4" t="s">
         <v>35</v>
@@ -858,13 +903,13 @@
         <v>11</v>
       </c>
       <c r="C5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F5" t="s">
         <v>35</v>
@@ -881,13 +926,13 @@
         <v>12</v>
       </c>
       <c r="C6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F6" t="s">
         <v>35</v>
@@ -904,13 +949,13 @@
         <v>13</v>
       </c>
       <c r="C7" t="s">
+        <v>58</v>
+      </c>
+      <c r="D7" t="s">
+        <v>57</v>
+      </c>
+      <c r="E7" t="s">
         <v>59</v>
-      </c>
-      <c r="D7" t="s">
-        <v>58</v>
-      </c>
-      <c r="E7" t="s">
-        <v>60</v>
       </c>
       <c r="F7" t="s">
         <v>30</v>
@@ -930,10 +975,10 @@
         <v>44</v>
       </c>
       <c r="D8" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E8" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>36</v>
@@ -953,10 +998,10 @@
         <v>44</v>
       </c>
       <c r="D9" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E9" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>36</v>
@@ -976,10 +1021,10 @@
         <v>44</v>
       </c>
       <c r="D10" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E10" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>36</v>
@@ -996,13 +1041,13 @@
         <v>17</v>
       </c>
       <c r="C11" t="s">
+        <v>74</v>
+      </c>
+      <c r="E11" t="s">
         <v>75</v>
       </c>
-      <c r="E11" t="s">
+      <c r="F11" s="2" t="s">
         <v>76</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>77</v>
       </c>
       <c r="G11">
         <v>47</v>
@@ -1016,10 +1061,13 @@
         <v>18</v>
       </c>
       <c r="C12" t="s">
-        <v>75</v>
+        <v>74</v>
+      </c>
+      <c r="E12" t="s">
+        <v>124</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G12">
         <v>47</v>
@@ -1033,13 +1081,13 @@
         <v>19</v>
       </c>
       <c r="C13" t="s">
+        <v>78</v>
+      </c>
+      <c r="D13" t="s">
         <v>79</v>
       </c>
-      <c r="D13" t="s">
+      <c r="E13" t="s">
         <v>80</v>
-      </c>
-      <c r="E13" t="s">
-        <v>81</v>
       </c>
       <c r="G13">
         <v>11</v>
@@ -1053,13 +1101,13 @@
         <v>20</v>
       </c>
       <c r="C14" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E14" t="s">
+        <v>81</v>
+      </c>
+      <c r="F14" t="s">
         <v>82</v>
-      </c>
-      <c r="F14" t="s">
-        <v>83</v>
       </c>
       <c r="G14">
         <v>45</v>
@@ -1073,13 +1121,13 @@
         <v>21</v>
       </c>
       <c r="C15" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D15" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E15" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F15" t="s">
         <v>30</v>
@@ -1096,13 +1144,13 @@
         <v>22</v>
       </c>
       <c r="C16" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D16" t="s">
+        <v>84</v>
+      </c>
+      <c r="E16" t="s">
         <v>85</v>
-      </c>
-      <c r="E16" t="s">
-        <v>86</v>
       </c>
       <c r="F16" t="s">
         <v>30</v>
@@ -1119,13 +1167,13 @@
         <v>23</v>
       </c>
       <c r="C17" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D17" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E17" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F17" t="s">
         <v>30</v>
@@ -1142,13 +1190,13 @@
         <v>24</v>
       </c>
       <c r="C18" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E18" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G18">
         <v>51</v>
@@ -1162,13 +1210,13 @@
         <v>25</v>
       </c>
       <c r="C19" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D19" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E19" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G19">
         <v>51</v>
@@ -1182,13 +1230,13 @@
         <v>26</v>
       </c>
       <c r="C20" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D20" t="s">
+        <v>93</v>
+      </c>
+      <c r="E20" t="s">
         <v>94</v>
-      </c>
-      <c r="E20" t="s">
-        <v>95</v>
       </c>
       <c r="G20">
         <v>51</v>
@@ -1202,13 +1250,13 @@
         <v>27</v>
       </c>
       <c r="C21" t="s">
+        <v>96</v>
+      </c>
+      <c r="D21" t="s">
+        <v>95</v>
+      </c>
+      <c r="E21" t="s">
         <v>97</v>
-      </c>
-      <c r="D21" t="s">
-        <v>96</v>
-      </c>
-      <c r="E21" t="s">
-        <v>98</v>
       </c>
       <c r="G21">
         <v>91</v>
@@ -1222,13 +1270,13 @@
         <v>28</v>
       </c>
       <c r="C22" t="s">
+        <v>96</v>
+      </c>
+      <c r="D22" t="s">
+        <v>98</v>
+      </c>
+      <c r="E22" t="s">
         <v>97</v>
-      </c>
-      <c r="D22" t="s">
-        <v>99</v>
-      </c>
-      <c r="E22" t="s">
-        <v>98</v>
       </c>
       <c r="G22">
         <v>91</v>
@@ -1242,13 +1290,13 @@
         <v>29</v>
       </c>
       <c r="C23" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D23" t="s">
+        <v>99</v>
+      </c>
+      <c r="E23" t="s">
         <v>100</v>
-      </c>
-      <c r="E23" t="s">
-        <v>101</v>
       </c>
       <c r="G23">
         <v>92</v>
@@ -1262,13 +1310,13 @@
         <v>30</v>
       </c>
       <c r="C24" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D24" t="s">
+        <v>101</v>
+      </c>
+      <c r="E24" t="s">
         <v>102</v>
-      </c>
-      <c r="E24" t="s">
-        <v>103</v>
       </c>
       <c r="G24">
         <v>8</v>
@@ -1285,10 +1333,10 @@
         <v>40</v>
       </c>
       <c r="D25" t="s">
+        <v>103</v>
+      </c>
+      <c r="E25" s="3" t="s">
         <v>104</v>
-      </c>
-      <c r="E25" s="3" t="s">
-        <v>105</v>
       </c>
       <c r="G25">
         <v>9</v>
@@ -1302,13 +1350,13 @@
         <v>32</v>
       </c>
       <c r="C26" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D26" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E26" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F26" t="s">
         <v>30</v>
@@ -1325,16 +1373,122 @@
         <v>33</v>
       </c>
       <c r="C27" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E27" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="F27" t="s">
         <v>107</v>
-      </c>
-      <c r="F27" t="s">
-        <v>108</v>
       </c>
       <c r="G27">
         <v>43</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>7</v>
+      </c>
+      <c r="B28" t="s">
+        <v>111</v>
+      </c>
+      <c r="C28" t="s">
+        <v>74</v>
+      </c>
+      <c r="E28" t="s">
+        <v>109</v>
+      </c>
+      <c r="F28" t="s">
+        <v>110</v>
+      </c>
+      <c r="G28">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
+        <v>7</v>
+      </c>
+      <c r="B29" t="s">
+        <v>114</v>
+      </c>
+      <c r="C29" t="s">
+        <v>74</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="F29" t="s">
+        <v>113</v>
+      </c>
+      <c r="G29">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>7</v>
+      </c>
+      <c r="B30" t="s">
+        <v>117</v>
+      </c>
+      <c r="C30" t="s">
+        <v>58</v>
+      </c>
+      <c r="D30" t="s">
+        <v>116</v>
+      </c>
+      <c r="E30" t="s">
+        <v>109</v>
+      </c>
+      <c r="F30" t="s">
+        <v>33</v>
+      </c>
+      <c r="G30">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
+        <v>7</v>
+      </c>
+      <c r="B31" t="s">
+        <v>119</v>
+      </c>
+      <c r="C31" t="s">
+        <v>74</v>
+      </c>
+      <c r="E31" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="F31" t="s">
+        <v>123</v>
+      </c>
+      <c r="G31">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A32" t="s">
+        <v>7</v>
+      </c>
+      <c r="B32" t="s">
+        <v>120</v>
+      </c>
+      <c r="C32" t="s">
+        <v>58</v>
+      </c>
+      <c r="D32" t="s">
+        <v>118</v>
+      </c>
+      <c r="E32" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="F32" t="s">
+        <v>119</v>
+      </c>
+      <c r="G32">
+        <v>70</v>
       </c>
     </row>
   </sheetData>
@@ -1370,7 +1524,7 @@
         <v>6</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
@@ -1384,10 +1538,10 @@
         <v>45</v>
       </c>
       <c r="D2" t="s">
+        <v>115</v>
+      </c>
+      <c r="E2" t="s">
         <v>46</v>
-      </c>
-      <c r="E2" t="s">
-        <v>47</v>
       </c>
       <c r="F2" t="s">
         <v>30</v>
@@ -1407,10 +1561,10 @@
         <v>45</v>
       </c>
       <c r="D3" t="s">
+        <v>55</v>
+      </c>
+      <c r="E3" t="s">
         <v>56</v>
-      </c>
-      <c r="E3" t="s">
-        <v>57</v>
       </c>
       <c r="F3" t="s">
         <v>30</v>
@@ -1427,13 +1581,13 @@
         <v>37</v>
       </c>
       <c r="C4" t="s">
+        <v>67</v>
+      </c>
+      <c r="D4" t="s">
         <v>68</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>69</v>
-      </c>
-      <c r="E4" t="s">
-        <v>70</v>
       </c>
       <c r="F4" t="s">
         <v>36</v>
@@ -1450,13 +1604,13 @@
         <v>38</v>
       </c>
       <c r="C5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D5" t="s">
+        <v>70</v>
+      </c>
+      <c r="E5" s="3" t="s">
         <v>71</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>72</v>
       </c>
       <c r="F5" t="s">
         <v>30</v>
@@ -1473,13 +1627,13 @@
         <v>39</v>
       </c>
       <c r="C6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D6" t="s">
+        <v>72</v>
+      </c>
+      <c r="E6" t="s">
         <v>73</v>
-      </c>
-      <c r="E6" t="s">
-        <v>74</v>
       </c>
       <c r="F6" t="s">
         <v>30</v>
